--- a/data-raw/tourism/trv-meta.xlsx
+++ b/data-raw/tourism/trv-meta.xlsx
@@ -10,7 +10,8 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="578" documentId="8_{B9F33ECC-A38F-1D4A-948E-E8A8617C5B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D992E1D2-8AA8-B344-92FD-C2CE4A09DB44}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{ADFBA318-8719-644D-899E-C1FCF3EFA216}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="15120" windowHeight="18980" xr2:uid="{ADFBA318-8719-644D-899E-C1FCF3EFA216}"/>
+    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="18980" activeTab="1" xr2:uid="{92BCB5F8-14FE-464F-8B9C-705BCCC79AFB}"/>
   </bookViews>
   <sheets>
     <sheet name="stopover_activity" sheetId="1" r:id="rId1"/>
